--- a/00-Administratif/01-AGENDA-25-26-eleve.xlsx
+++ b/00-Administratif/01-AGENDA-25-26-eleve.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B967F0-5876-49B2-B807-EC4F1FBEF4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50527E7C-029A-4062-8150-44FBE294BC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2800" yWindow="1945" windowWidth="14400" windowHeight="7455" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Résumé" sheetId="4" state="hidden" r:id="rId1"/>
@@ -1472,38 +1472,59 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1529,25 +1550,49 @@
     <xf numFmtId="0" fontId="15" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1574,42 +1619,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1638,15 +1647,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="5" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2627,28 +2627,28 @@
       <c r="T2" s="78"/>
     </row>
     <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="129" t="s">
+      <c r="A3" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
       <c r="K3" s="78"/>
-      <c r="L3" s="126" t="s">
+      <c r="L3" s="130" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="Q3" s="130"/>
       <c r="R3" s="78"/>
-      <c r="S3" s="120" t="s">
+      <c r="S3" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="121"/>
+      <c r="T3" s="129"/>
     </row>
     <row r="4" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21">
@@ -3577,11 +3577,11 @@
     </row>
     <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28"/>
-      <c r="B27" s="130" t="s">
+      <c r="B27" s="127" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="130"/>
-      <c r="D27" s="130"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="127"/>
       <c r="E27" s="28"/>
       <c r="F27" s="78"/>
       <c r="K27" s="78"/>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="28"/>
-      <c r="B32" s="127" t="s">
+      <c r="B32" s="120" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="128"/>
+      <c r="C32" s="121"/>
       <c r="D32" s="28"/>
       <c r="E32" s="28"/>
       <c r="F32" s="78"/>
@@ -3709,12 +3709,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B27:D27"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="K28:L28"/>
     <mergeCell ref="K30:L30"/>
@@ -3722,6 +3716,12 @@
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="L3:Q3"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B27:D27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="34_1!A1" display="34_1!A1" xr:uid="{287AAE1E-E741-4AEB-AC8F-F90539215C59}"/>
@@ -3786,28 +3786,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="131" t="s">
+      <c r="C1" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="131" t="s">
+      <c r="D1" s="138" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="133" t="s">
+      <c r="F1" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="133"/>
-      <c r="H1" s="134"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="141"/>
       <c r="I1" s="65"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
     <row r="2" spans="3:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
       <c r="E2" s="58" t="s">
         <v>4</v>
       </c>
@@ -3824,14 +3824,14 @@
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="3:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="135" t="s">
+      <c r="C3" s="142" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="142"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="142"/>
+      <c r="H3" s="142"/>
       <c r="I3" s="65"/>
       <c r="P3" s="1"/>
     </row>
@@ -3855,7 +3855,7 @@
       <c r="H4" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="139" t="s">
+      <c r="I4" s="135" t="s">
         <v>32</v>
       </c>
       <c r="J4" s="119" t="s">
@@ -3870,7 +3870,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="43"/>
       <c r="H5" s="63"/>
-      <c r="I5" s="140"/>
+      <c r="I5" s="136"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
@@ -3882,7 +3882,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="43"/>
       <c r="H6" s="63"/>
-      <c r="I6" s="140"/>
+      <c r="I6" s="136"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3906,7 +3906,7 @@
       <c r="H7" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="139" t="s">
+      <c r="I7" s="135" t="s">
         <v>33</v>
       </c>
       <c r="P7" s="1"/>
@@ -3918,7 +3918,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="43"/>
       <c r="H8" s="63"/>
-      <c r="I8" s="140"/>
+      <c r="I8" s="136"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="3:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3928,12 +3928,12 @@
       <c r="F9" s="3"/>
       <c r="G9" s="43"/>
       <c r="H9" s="63"/>
-      <c r="I9" s="140"/>
+      <c r="I9" s="136"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="142" t="s">
+      <c r="N9" s="131" t="s">
         <v>9</v>
       </c>
-      <c r="O9" s="143"/>
+      <c r="O9" s="132"/>
     </row>
     <row r="10" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C10" s="37"/>
@@ -3942,7 +3942,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="43"/>
       <c r="H10" s="63"/>
-      <c r="I10" s="140"/>
+      <c r="I10" s="136"/>
       <c r="M10" s="1"/>
       <c r="N10" s="10"/>
       <c r="O10" s="11"/>
@@ -3954,7 +3954,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="43"/>
       <c r="H11" s="63"/>
-      <c r="I11" s="140"/>
+      <c r="I11" s="136"/>
       <c r="M11" s="1"/>
       <c r="N11" s="72">
         <v>0.33333333333333331</v>
@@ -3971,7 +3971,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="43"/>
       <c r="H12" s="63"/>
-      <c r="I12" s="141"/>
+      <c r="I12" s="137"/>
       <c r="M12" s="1"/>
       <c r="N12" s="72">
         <v>0.36805555555555558</v>
@@ -4019,7 +4019,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="43"/>
       <c r="H14" s="46"/>
-      <c r="I14" s="139" t="s">
+      <c r="I14" s="135" t="s">
         <v>34</v>
       </c>
       <c r="M14" s="1"/>
@@ -4038,7 +4038,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="43"/>
       <c r="H15" s="46"/>
-      <c r="I15" s="140"/>
+      <c r="I15" s="136"/>
       <c r="M15" s="1"/>
       <c r="N15" s="72">
         <v>0.47916666666666669</v>
@@ -4055,7 +4055,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="43"/>
       <c r="H16" s="46"/>
-      <c r="I16" s="140"/>
+      <c r="I16" s="136"/>
       <c r="M16" s="1"/>
       <c r="N16" s="72"/>
       <c r="O16" s="73"/>
@@ -4067,7 +4067,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="43"/>
       <c r="H17" s="46"/>
-      <c r="I17" s="140"/>
+      <c r="I17" s="136"/>
       <c r="M17" s="1"/>
       <c r="N17" s="72">
         <v>0.51388888888888895</v>
@@ -4084,7 +4084,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="43"/>
       <c r="H18" s="46"/>
-      <c r="I18" s="141"/>
+      <c r="I18" s="137"/>
       <c r="M18" s="1"/>
       <c r="N18" s="72"/>
       <c r="O18" s="73"/>
@@ -4127,7 +4127,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="43"/>
       <c r="H20" s="46"/>
-      <c r="I20" s="139" t="s">
+      <c r="I20" s="135" t="s">
         <v>34</v>
       </c>
       <c r="M20" s="1"/>
@@ -4146,7 +4146,7 @@
       <c r="F21" s="3"/>
       <c r="G21" s="43"/>
       <c r="H21" s="46"/>
-      <c r="I21" s="140"/>
+      <c r="I21" s="136"/>
       <c r="M21" s="1"/>
       <c r="N21" s="72">
         <v>0.625</v>
@@ -4163,7 +4163,7 @@
       <c r="F22" s="3"/>
       <c r="G22" s="43"/>
       <c r="H22" s="46"/>
-      <c r="I22" s="140"/>
+      <c r="I22" s="136"/>
       <c r="M22" s="1"/>
       <c r="N22" s="72">
         <v>0.65972222222222221</v>
@@ -4180,7 +4180,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="43"/>
       <c r="H23" s="46"/>
-      <c r="I23" s="140"/>
+      <c r="I23" s="136"/>
       <c r="M23" s="1"/>
       <c r="N23" s="72">
         <v>0.69444444444444453</v>
@@ -4197,7 +4197,7 @@
       <c r="F24" s="3"/>
       <c r="G24" s="43"/>
       <c r="H24" s="46"/>
-      <c r="I24" s="141"/>
+      <c r="I24" s="137"/>
       <c r="M24" s="1"/>
       <c r="N24" s="74">
         <v>0.72916666666666663</v>
@@ -4237,7 +4237,7 @@
       <c r="F26" s="3"/>
       <c r="G26" s="43"/>
       <c r="H26" s="46"/>
-      <c r="I26" s="139" t="s">
+      <c r="I26" s="135" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       <c r="F27" s="3"/>
       <c r="G27" s="43"/>
       <c r="H27" s="46"/>
-      <c r="I27" s="140"/>
+      <c r="I27" s="136"/>
     </row>
     <row r="28" spans="3:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="37"/>
@@ -4257,7 +4257,7 @@
       <c r="F28" s="3"/>
       <c r="G28" s="43"/>
       <c r="H28" s="46"/>
-      <c r="I28" s="140"/>
+      <c r="I28" s="136"/>
     </row>
     <row r="29" spans="3:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="37"/>
@@ -4266,7 +4266,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="43"/>
       <c r="H29" s="46"/>
-      <c r="I29" s="140"/>
+      <c r="I29" s="136"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
@@ -4278,7 +4278,7 @@
       <c r="F30" s="3"/>
       <c r="G30" s="43"/>
       <c r="H30" s="46"/>
-      <c r="I30" s="141"/>
+      <c r="I30" s="137"/>
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="3:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4314,7 +4314,7 @@
       <c r="F32" s="3"/>
       <c r="G32" s="43"/>
       <c r="H32" s="46"/>
-      <c r="I32" s="139" t="s">
+      <c r="I32" s="135" t="s">
         <v>34</v>
       </c>
       <c r="P32" s="1"/>
@@ -4326,7 +4326,7 @@
       <c r="F33" s="3"/>
       <c r="G33" s="43"/>
       <c r="H33" s="46"/>
-      <c r="I33" s="140"/>
+      <c r="I33" s="136"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
@@ -4338,7 +4338,7 @@
       <c r="F34" s="3"/>
       <c r="G34" s="43"/>
       <c r="H34" s="46"/>
-      <c r="I34" s="140"/>
+      <c r="I34" s="136"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
@@ -4350,7 +4350,7 @@
       <c r="F35" s="3"/>
       <c r="G35" s="43"/>
       <c r="H35" s="46"/>
-      <c r="I35" s="140"/>
+      <c r="I35" s="136"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
@@ -4362,7 +4362,7 @@
       <c r="F36" s="3"/>
       <c r="G36" s="43"/>
       <c r="H36" s="46"/>
-      <c r="I36" s="141"/>
+      <c r="I36" s="137"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
@@ -4412,7 +4412,7 @@
       <c r="F39" s="3"/>
       <c r="G39" s="43"/>
       <c r="H39" s="46"/>
-      <c r="I39" s="139" t="s">
+      <c r="I39" s="135" t="s">
         <v>34</v>
       </c>
       <c r="P39" s="1"/>
@@ -4426,7 +4426,7 @@
       <c r="F40" s="3"/>
       <c r="G40" s="43"/>
       <c r="H40" s="46"/>
-      <c r="I40" s="140"/>
+      <c r="I40" s="136"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
@@ -4438,7 +4438,7 @@
       <c r="F41" s="3"/>
       <c r="G41" s="43"/>
       <c r="H41" s="46"/>
-      <c r="I41" s="140"/>
+      <c r="I41" s="136"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
@@ -4450,7 +4450,7 @@
       <c r="F42" s="3"/>
       <c r="G42" s="43"/>
       <c r="H42" s="46"/>
-      <c r="I42" s="140"/>
+      <c r="I42" s="136"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
@@ -4462,7 +4462,7 @@
       <c r="F43" s="3"/>
       <c r="G43" s="43"/>
       <c r="H43" s="46"/>
-      <c r="I43" s="141"/>
+      <c r="I43" s="137"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
@@ -4500,7 +4500,7 @@
       <c r="F45" s="3"/>
       <c r="G45" s="43"/>
       <c r="H45" s="46"/>
-      <c r="I45" s="139" t="s">
+      <c r="I45" s="135" t="s">
         <v>34</v>
       </c>
       <c r="P45" s="1"/>
@@ -4514,7 +4514,7 @@
       <c r="F46" s="3"/>
       <c r="G46" s="43"/>
       <c r="H46" s="46"/>
-      <c r="I46" s="140"/>
+      <c r="I46" s="136"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
@@ -4526,7 +4526,7 @@
       <c r="F47" s="3"/>
       <c r="G47" s="43"/>
       <c r="H47" s="46"/>
-      <c r="I47" s="140"/>
+      <c r="I47" s="136"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
@@ -4538,7 +4538,7 @@
       <c r="F48" s="3"/>
       <c r="G48" s="43"/>
       <c r="H48" s="46"/>
-      <c r="I48" s="140"/>
+      <c r="I48" s="136"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
@@ -4550,7 +4550,7 @@
       <c r="F49" s="3"/>
       <c r="G49" s="43"/>
       <c r="H49" s="46"/>
-      <c r="I49" s="141"/>
+      <c r="I49" s="137"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
@@ -4652,7 +4652,7 @@
       <c r="F54" s="3"/>
       <c r="G54" s="43"/>
       <c r="H54" s="46"/>
-      <c r="I54" s="139" t="s">
+      <c r="I54" s="135" t="s">
         <v>34</v>
       </c>
       <c r="P54" s="1"/>
@@ -4666,7 +4666,7 @@
       <c r="F55" s="3"/>
       <c r="G55" s="43"/>
       <c r="H55" s="46"/>
-      <c r="I55" s="140"/>
+      <c r="I55" s="136"/>
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
@@ -4678,7 +4678,7 @@
       <c r="F56" s="3"/>
       <c r="G56" s="43"/>
       <c r="H56" s="46"/>
-      <c r="I56" s="140"/>
+      <c r="I56" s="136"/>
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
@@ -4690,7 +4690,7 @@
       <c r="F57" s="3"/>
       <c r="G57" s="43"/>
       <c r="H57" s="46"/>
-      <c r="I57" s="140"/>
+      <c r="I57" s="136"/>
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
@@ -4702,7 +4702,7 @@
       <c r="F58" s="3"/>
       <c r="G58" s="43"/>
       <c r="H58" s="46"/>
-      <c r="I58" s="141"/>
+      <c r="I58" s="137"/>
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
@@ -4770,7 +4770,7 @@
       <c r="F62" s="3"/>
       <c r="G62" s="43"/>
       <c r="H62" s="46"/>
-      <c r="I62" s="139" t="s">
+      <c r="I62" s="135" t="s">
         <v>34</v>
       </c>
       <c r="J62" s="7"/>
@@ -4790,7 +4790,7 @@
       <c r="F63" s="3"/>
       <c r="G63" s="43"/>
       <c r="H63" s="46"/>
-      <c r="I63" s="140"/>
+      <c r="I63" s="136"/>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -4808,7 +4808,7 @@
       <c r="F64" s="3"/>
       <c r="G64" s="43"/>
       <c r="H64" s="46"/>
-      <c r="I64" s="140"/>
+      <c r="I64" s="136"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -4826,7 +4826,7 @@
       <c r="F65" s="3"/>
       <c r="G65" s="43"/>
       <c r="H65" s="46"/>
-      <c r="I65" s="140"/>
+      <c r="I65" s="136"/>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -4844,7 +4844,7 @@
       <c r="F66" s="3"/>
       <c r="G66" s="43"/>
       <c r="H66" s="46"/>
-      <c r="I66" s="141"/>
+      <c r="I66" s="137"/>
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -4912,7 +4912,7 @@
       <c r="F69" s="3"/>
       <c r="G69" s="43"/>
       <c r="H69" s="46"/>
-      <c r="I69" s="139" t="s">
+      <c r="I69" s="135" t="s">
         <v>34</v>
       </c>
       <c r="J69" s="7"/>
@@ -4932,7 +4932,7 @@
       <c r="F70" s="3"/>
       <c r="G70" s="43"/>
       <c r="H70" s="46"/>
-      <c r="I70" s="140"/>
+      <c r="I70" s="136"/>
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -4950,7 +4950,7 @@
       <c r="F71" s="3"/>
       <c r="G71" s="43"/>
       <c r="H71" s="46"/>
-      <c r="I71" s="140"/>
+      <c r="I71" s="136"/>
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -4968,7 +4968,7 @@
       <c r="F72" s="3"/>
       <c r="G72" s="43"/>
       <c r="H72" s="46"/>
-      <c r="I72" s="140"/>
+      <c r="I72" s="136"/>
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -4986,7 +4986,7 @@
       <c r="F73" s="3"/>
       <c r="G73" s="43"/>
       <c r="H73" s="46"/>
-      <c r="I73" s="141"/>
+      <c r="I73" s="137"/>
       <c r="J73" s="7"/>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -5054,7 +5054,7 @@
       <c r="F76" s="3"/>
       <c r="G76" s="43"/>
       <c r="H76" s="46"/>
-      <c r="I76" s="139" t="s">
+      <c r="I76" s="135" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5065,7 +5065,7 @@
       <c r="F77" s="3"/>
       <c r="G77" s="43"/>
       <c r="H77" s="46"/>
-      <c r="I77" s="140"/>
+      <c r="I77" s="136"/>
     </row>
     <row r="78" spans="3:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="37"/>
@@ -5074,7 +5074,7 @@
       <c r="F78" s="3"/>
       <c r="G78" s="43"/>
       <c r="H78" s="46"/>
-      <c r="I78" s="140"/>
+      <c r="I78" s="136"/>
     </row>
     <row r="79" spans="3:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C79" s="37"/>
@@ -5083,7 +5083,7 @@
       <c r="F79" s="3"/>
       <c r="G79" s="43"/>
       <c r="H79" s="46"/>
-      <c r="I79" s="140"/>
+      <c r="I79" s="136"/>
     </row>
     <row r="80" spans="3:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C80" s="37"/>
@@ -5092,7 +5092,7 @@
       <c r="F80" s="3"/>
       <c r="G80" s="43"/>
       <c r="H80" s="46"/>
-      <c r="I80" s="141"/>
+      <c r="I80" s="137"/>
     </row>
     <row r="81" spans="3:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C81" s="37">
@@ -5124,7 +5124,7 @@
       <c r="F82" s="3"/>
       <c r="G82" s="43"/>
       <c r="H82" s="46"/>
-      <c r="I82" s="139" t="s">
+      <c r="I82" s="135" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       <c r="F83" s="3"/>
       <c r="G83" s="43"/>
       <c r="H83" s="46"/>
-      <c r="I83" s="140"/>
+      <c r="I83" s="136"/>
     </row>
     <row r="84" spans="3:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C84" s="37"/>
@@ -5144,7 +5144,7 @@
       <c r="F84" s="3"/>
       <c r="G84" s="43"/>
       <c r="H84" s="46"/>
-      <c r="I84" s="140"/>
+      <c r="I84" s="136"/>
     </row>
     <row r="85" spans="3:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C85" s="37"/>
@@ -5153,7 +5153,7 @@
       <c r="F85" s="3"/>
       <c r="G85" s="43"/>
       <c r="H85" s="46"/>
-      <c r="I85" s="140"/>
+      <c r="I85" s="136"/>
     </row>
     <row r="86" spans="3:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C86" s="37"/>
@@ -5162,7 +5162,7 @@
       <c r="F86" s="3"/>
       <c r="G86" s="43"/>
       <c r="H86" s="46"/>
-      <c r="I86" s="141"/>
+      <c r="I86" s="137"/>
     </row>
     <row r="87" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C87" s="37">
@@ -5194,7 +5194,7 @@
       <c r="F88" s="3"/>
       <c r="G88" s="43"/>
       <c r="H88" s="46"/>
-      <c r="I88" s="139" t="s">
+      <c r="I88" s="135" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
       <c r="F89" s="3"/>
       <c r="G89" s="43"/>
       <c r="H89" s="46"/>
-      <c r="I89" s="140"/>
+      <c r="I89" s="136"/>
     </row>
     <row r="90" spans="3:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="37"/>
@@ -5214,7 +5214,7 @@
       <c r="F90" s="3"/>
       <c r="G90" s="43"/>
       <c r="H90" s="46"/>
-      <c r="I90" s="140"/>
+      <c r="I90" s="136"/>
     </row>
     <row r="91" spans="3:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C91" s="37"/>
@@ -5223,7 +5223,7 @@
       <c r="F91" s="3"/>
       <c r="G91" s="43"/>
       <c r="H91" s="46"/>
-      <c r="I91" s="140"/>
+      <c r="I91" s="136"/>
     </row>
     <row r="92" spans="3:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C92" s="37"/>
@@ -5232,7 +5232,7 @@
       <c r="F92" s="3"/>
       <c r="G92" s="43"/>
       <c r="H92" s="46"/>
-      <c r="I92" s="141"/>
+      <c r="I92" s="137"/>
     </row>
     <row r="93" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C93" s="37">
@@ -5264,7 +5264,7 @@
       <c r="F94" s="3"/>
       <c r="G94" s="43"/>
       <c r="H94" s="46"/>
-      <c r="I94" s="139" t="s">
+      <c r="I94" s="135" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       <c r="F95" s="3"/>
       <c r="G95" s="43"/>
       <c r="H95" s="46"/>
-      <c r="I95" s="140"/>
+      <c r="I95" s="136"/>
     </row>
     <row r="96" spans="3:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="37"/>
@@ -5284,7 +5284,7 @@
       <c r="F96" s="3"/>
       <c r="G96" s="43"/>
       <c r="H96" s="46"/>
-      <c r="I96" s="140"/>
+      <c r="I96" s="136"/>
     </row>
     <row r="97" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C97" s="37"/>
@@ -5293,7 +5293,7 @@
       <c r="F97" s="3"/>
       <c r="G97" s="43"/>
       <c r="H97" s="46"/>
-      <c r="I97" s="140"/>
+      <c r="I97" s="136"/>
     </row>
     <row r="98" spans="3:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C98" s="37"/>
@@ -5302,7 +5302,7 @@
       <c r="F98" s="3"/>
       <c r="G98" s="43"/>
       <c r="H98" s="46"/>
-      <c r="I98" s="141"/>
+      <c r="I98" s="137"/>
     </row>
     <row r="99" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C99" s="37">
@@ -5332,7 +5332,7 @@
       <c r="F100" s="3"/>
       <c r="G100" s="43"/>
       <c r="H100" s="46"/>
-      <c r="I100" s="139" t="s">
+      <c r="I100" s="135" t="s">
         <v>34</v>
       </c>
       <c r="J100" s="118"/>
@@ -5344,7 +5344,7 @@
       <c r="F101" s="3"/>
       <c r="G101" s="43"/>
       <c r="H101" s="46"/>
-      <c r="I101" s="140"/>
+      <c r="I101" s="136"/>
       <c r="J101" s="116" t="s">
         <v>81</v>
       </c>
@@ -5356,7 +5356,7 @@
       <c r="F102" s="3"/>
       <c r="G102" s="43"/>
       <c r="H102" s="46"/>
-      <c r="I102" s="140"/>
+      <c r="I102" s="136"/>
       <c r="J102" s="117"/>
     </row>
     <row r="103" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5366,7 +5366,7 @@
       <c r="F103" s="3"/>
       <c r="G103" s="43"/>
       <c r="H103" s="46"/>
-      <c r="I103" s="140"/>
+      <c r="I103" s="136"/>
       <c r="J103" s="116" t="s">
         <v>82</v>
       </c>
@@ -5378,7 +5378,7 @@
       <c r="F104" s="3"/>
       <c r="G104" s="43"/>
       <c r="H104" s="46"/>
-      <c r="I104" s="141"/>
+      <c r="I104" s="137"/>
     </row>
     <row r="105" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C105" s="39">
@@ -5454,7 +5454,7 @@
       <c r="F108" s="3"/>
       <c r="G108" s="43"/>
       <c r="H108" s="47"/>
-      <c r="I108" s="139" t="s">
+      <c r="I108" s="135" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       <c r="F109" s="3"/>
       <c r="G109" s="43"/>
       <c r="H109" s="47"/>
-      <c r="I109" s="140"/>
+      <c r="I109" s="136"/>
     </row>
     <row r="110" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C110" s="37"/>
@@ -5474,7 +5474,7 @@
       <c r="F110" s="3"/>
       <c r="G110" s="43"/>
       <c r="H110" s="47"/>
-      <c r="I110" s="140"/>
+      <c r="I110" s="136"/>
     </row>
     <row r="111" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C111" s="37"/>
@@ -5483,7 +5483,7 @@
       <c r="F111" s="3"/>
       <c r="G111" s="43"/>
       <c r="H111" s="47"/>
-      <c r="I111" s="140"/>
+      <c r="I111" s="136"/>
     </row>
     <row r="112" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C112" s="37"/>
@@ -5492,7 +5492,7 @@
       <c r="F112" s="3"/>
       <c r="G112" s="43"/>
       <c r="H112" s="47"/>
-      <c r="I112" s="141"/>
+      <c r="I112" s="137"/>
     </row>
     <row r="113" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C113" s="37"/>
@@ -5533,7 +5533,7 @@
       <c r="F115" s="3"/>
       <c r="G115" s="43"/>
       <c r="H115" s="46"/>
-      <c r="I115" s="136" t="s">
+      <c r="I115" s="143" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       <c r="F116" s="3"/>
       <c r="G116" s="43"/>
       <c r="H116" s="46"/>
-      <c r="I116" s="137"/>
+      <c r="I116" s="144"/>
     </row>
     <row r="117" spans="3:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C117" s="37"/>
@@ -5553,7 +5553,7 @@
       <c r="F117" s="3"/>
       <c r="G117" s="43"/>
       <c r="H117" s="46"/>
-      <c r="I117" s="137"/>
+      <c r="I117" s="144"/>
     </row>
     <row r="118" spans="3:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C118" s="37"/>
@@ -5562,7 +5562,7 @@
       <c r="F118" s="3"/>
       <c r="G118" s="43"/>
       <c r="H118" s="46"/>
-      <c r="I118" s="137"/>
+      <c r="I118" s="144"/>
     </row>
     <row r="119" spans="3:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C119" s="37"/>
@@ -5571,7 +5571,7 @@
       <c r="F119" s="3"/>
       <c r="G119" s="43"/>
       <c r="H119" s="46"/>
-      <c r="I119" s="138"/>
+      <c r="I119" s="145"/>
     </row>
     <row r="120" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C120" s="44"/>
@@ -5584,10 +5584,10 @@
     </row>
     <row r="121" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C121" s="44"/>
-      <c r="D121" s="144" t="s">
+      <c r="D121" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="E121" s="144"/>
+      <c r="E121" s="133"/>
       <c r="F121" s="7"/>
       <c r="G121" s="44"/>
       <c r="H121" s="49"/>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="126" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C126" s="44"/>
-      <c r="D126" s="145" t="s">
+      <c r="D126" s="134" t="s">
         <v>30</v>
       </c>
-      <c r="E126" s="145"/>
+      <c r="E126" s="134"/>
       <c r="F126" s="7"/>
       <c r="G126" s="44"/>
       <c r="H126" s="49"/>
@@ -5663,6 +5663,16 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I115:I119"/>
+    <mergeCell ref="I108:I112"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I7:I12"/>
+    <mergeCell ref="I14:I18"/>
+    <mergeCell ref="I20:I24"/>
     <mergeCell ref="N9:O9"/>
     <mergeCell ref="D121:E121"/>
     <mergeCell ref="D126:E126"/>
@@ -5678,16 +5688,6 @@
     <mergeCell ref="I88:I92"/>
     <mergeCell ref="I94:I98"/>
     <mergeCell ref="I100:I104"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I115:I119"/>
-    <mergeCell ref="I108:I112"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I7:I12"/>
-    <mergeCell ref="I14:I18"/>
-    <mergeCell ref="I20:I24"/>
   </mergeCells>
   <phoneticPr fontId="38" type="noConversion"/>
   <hyperlinks>
@@ -5734,25 +5734,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:16" ht="18" x14ac:dyDescent="0.25">
-      <c r="C1" s="131" t="s">
+      <c r="C1" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="131" t="s">
+      <c r="D1" s="138" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="176" t="str">
+      <c r="F1" s="158" t="str">
         <f>'Semestre -1'!F1</f>
         <v>Tableau de numérotation des semaines</v>
       </c>
-      <c r="G1" s="176"/>
-      <c r="H1" s="177"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="159"/>
     </row>
     <row r="2" spans="3:16" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
       <c r="E2" s="42" t="s">
         <v>4</v>
       </c>
@@ -5774,14 +5774,14 @@
       <c r="H3" s="71"/>
     </row>
     <row r="4" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C4" s="178" t="s">
+      <c r="C4" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="178"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
     </row>
     <row r="5" spans="3:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" s="37">
@@ -5813,10 +5813,10 @@
       <c r="F6" s="3"/>
       <c r="G6" s="43"/>
       <c r="H6" s="46"/>
-      <c r="I6" s="154" t="s">
+      <c r="I6" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="155"/>
+      <c r="J6" s="147"/>
     </row>
     <row r="7" spans="3:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="37"/>
@@ -5825,8 +5825,8 @@
       <c r="F7" s="3"/>
       <c r="G7" s="43"/>
       <c r="H7" s="46"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="157"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="149"/>
     </row>
     <row r="8" spans="3:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="37"/>
@@ -5835,8 +5835,8 @@
       <c r="F8" s="3"/>
       <c r="G8" s="43"/>
       <c r="H8" s="46"/>
-      <c r="I8" s="156"/>
-      <c r="J8" s="157"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="149"/>
     </row>
     <row r="9" spans="3:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C9" s="37"/>
@@ -5845,8 +5845,8 @@
       <c r="F9" s="3"/>
       <c r="G9" s="43"/>
       <c r="H9" s="46"/>
-      <c r="I9" s="156"/>
-      <c r="J9" s="157"/>
+      <c r="I9" s="148"/>
+      <c r="J9" s="149"/>
     </row>
     <row r="10" spans="3:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="37"/>
@@ -5855,12 +5855,12 @@
       <c r="F10" s="3"/>
       <c r="G10" s="43"/>
       <c r="H10" s="46"/>
-      <c r="I10" s="158"/>
-      <c r="J10" s="159"/>
-      <c r="O10" s="142" t="s">
+      <c r="I10" s="150"/>
+      <c r="J10" s="151"/>
+      <c r="O10" s="131" t="s">
         <v>9</v>
       </c>
-      <c r="P10" s="143"/>
+      <c r="P10" s="132"/>
     </row>
     <row r="11" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C11" s="37">
@@ -5940,10 +5940,10 @@
       <c r="F14" s="3"/>
       <c r="G14" s="43"/>
       <c r="H14" s="46"/>
-      <c r="I14" s="154" t="s">
+      <c r="I14" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="155"/>
+      <c r="J14" s="147"/>
       <c r="O14" s="72">
         <v>0.40972222222222227</v>
       </c>
@@ -5959,8 +5959,8 @@
       <c r="F15" s="3"/>
       <c r="G15" s="43"/>
       <c r="H15" s="46"/>
-      <c r="I15" s="156"/>
-      <c r="J15" s="157"/>
+      <c r="I15" s="148"/>
+      <c r="J15" s="149"/>
       <c r="O15" s="72">
         <v>0.44444444444444442</v>
       </c>
@@ -5976,8 +5976,8 @@
       <c r="F16" s="3"/>
       <c r="G16" s="43"/>
       <c r="H16" s="46"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="157"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="149"/>
       <c r="O16" s="72">
         <v>0.47916666666666669</v>
       </c>
@@ -5993,8 +5993,8 @@
       <c r="F17" s="3"/>
       <c r="G17" s="43"/>
       <c r="H17" s="46"/>
-      <c r="I17" s="156"/>
-      <c r="J17" s="157"/>
+      <c r="I17" s="148"/>
+      <c r="J17" s="149"/>
       <c r="O17" s="72"/>
       <c r="P17" s="73"/>
     </row>
@@ -6005,8 +6005,8 @@
       <c r="F18" s="3"/>
       <c r="G18" s="43"/>
       <c r="H18" s="46"/>
-      <c r="I18" s="158"/>
-      <c r="J18" s="159"/>
+      <c r="I18" s="150"/>
+      <c r="J18" s="151"/>
       <c r="O18" s="72">
         <v>0.51388888888888895</v>
       </c>
@@ -6044,10 +6044,10 @@
       <c r="F20" s="3"/>
       <c r="G20" s="43"/>
       <c r="H20" s="43"/>
-      <c r="I20" s="154" t="s">
+      <c r="I20" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="J20" s="155"/>
+      <c r="J20" s="147"/>
       <c r="O20" s="72">
         <v>0.54861111111111105</v>
       </c>
@@ -6063,8 +6063,8 @@
       <c r="F21" s="3"/>
       <c r="G21" s="43"/>
       <c r="H21" s="46"/>
-      <c r="I21" s="156"/>
-      <c r="J21" s="157"/>
+      <c r="I21" s="148"/>
+      <c r="J21" s="149"/>
       <c r="O21" s="72">
         <v>0.59027777777777779</v>
       </c>
@@ -6080,8 +6080,8 @@
       <c r="F22" s="3"/>
       <c r="G22" s="43"/>
       <c r="H22" s="46"/>
-      <c r="I22" s="156"/>
-      <c r="J22" s="157"/>
+      <c r="I22" s="148"/>
+      <c r="J22" s="149"/>
       <c r="O22" s="72">
         <v>0.625</v>
       </c>
@@ -6097,8 +6097,8 @@
       <c r="F23" s="3"/>
       <c r="G23" s="43"/>
       <c r="H23" s="46"/>
-      <c r="I23" s="156"/>
-      <c r="J23" s="157"/>
+      <c r="I23" s="148"/>
+      <c r="J23" s="149"/>
       <c r="O23" s="72">
         <v>0.65972222222222221</v>
       </c>
@@ -6114,8 +6114,8 @@
       <c r="F24" s="3"/>
       <c r="G24" s="43"/>
       <c r="H24" s="46"/>
-      <c r="I24" s="158"/>
-      <c r="J24" s="159"/>
+      <c r="I24" s="150"/>
+      <c r="J24" s="151"/>
       <c r="O24" s="72">
         <v>0.69444444444444453</v>
       </c>
@@ -6162,10 +6162,10 @@
       <c r="F26" s="98"/>
       <c r="G26" s="97"/>
       <c r="H26" s="102"/>
-      <c r="I26" s="160" t="s">
+      <c r="I26" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="161"/>
+      <c r="J26" s="153"/>
       <c r="O26" s="12"/>
       <c r="P26" s="13"/>
     </row>
@@ -6176,8 +6176,8 @@
       <c r="F27" s="98"/>
       <c r="G27" s="97"/>
       <c r="H27" s="102"/>
-      <c r="I27" s="162"/>
-      <c r="J27" s="163"/>
+      <c r="I27" s="154"/>
+      <c r="J27" s="155"/>
     </row>
     <row r="28" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="37"/>
@@ -6186,8 +6186,8 @@
       <c r="F28" s="98"/>
       <c r="G28" s="97"/>
       <c r="H28" s="102"/>
-      <c r="I28" s="162"/>
-      <c r="J28" s="163"/>
+      <c r="I28" s="154"/>
+      <c r="J28" s="155"/>
     </row>
     <row r="29" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="37"/>
@@ -6196,8 +6196,8 @@
       <c r="F29" s="98"/>
       <c r="G29" s="97"/>
       <c r="H29" s="102"/>
-      <c r="I29" s="162"/>
-      <c r="J29" s="163"/>
+      <c r="I29" s="154"/>
+      <c r="J29" s="155"/>
     </row>
     <row r="30" spans="3:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C30" s="37"/>
@@ -6206,8 +6206,8 @@
       <c r="F30" s="98"/>
       <c r="G30" s="97"/>
       <c r="H30" s="102"/>
-      <c r="I30" s="164"/>
-      <c r="J30" s="165"/>
+      <c r="I30" s="156"/>
+      <c r="J30" s="157"/>
     </row>
     <row r="31" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C31" s="37"/>
@@ -6246,10 +6246,10 @@
       <c r="F33" s="3"/>
       <c r="G33" s="43"/>
       <c r="H33" s="46"/>
-      <c r="I33" s="154" t="s">
+      <c r="I33" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="J33" s="155"/>
+      <c r="J33" s="147"/>
     </row>
     <row r="34" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="37"/>
@@ -6258,8 +6258,8 @@
       <c r="F34" s="3"/>
       <c r="G34" s="43"/>
       <c r="H34" s="46"/>
-      <c r="I34" s="156"/>
-      <c r="J34" s="157"/>
+      <c r="I34" s="148"/>
+      <c r="J34" s="149"/>
     </row>
     <row r="35" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="37"/>
@@ -6268,8 +6268,8 @@
       <c r="F35" s="3"/>
       <c r="G35" s="43"/>
       <c r="H35" s="46"/>
-      <c r="I35" s="156"/>
-      <c r="J35" s="157"/>
+      <c r="I35" s="148"/>
+      <c r="J35" s="149"/>
     </row>
     <row r="36" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="37"/>
@@ -6278,8 +6278,8 @@
       <c r="F36" s="3"/>
       <c r="G36" s="43"/>
       <c r="H36" s="46"/>
-      <c r="I36" s="156"/>
-      <c r="J36" s="157"/>
+      <c r="I36" s="148"/>
+      <c r="J36" s="149"/>
     </row>
     <row r="37" spans="3:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C37" s="37"/>
@@ -6288,8 +6288,8 @@
       <c r="F37" s="3"/>
       <c r="G37" s="43"/>
       <c r="H37" s="46"/>
-      <c r="I37" s="158"/>
-      <c r="J37" s="159"/>
+      <c r="I37" s="150"/>
+      <c r="J37" s="151"/>
     </row>
     <row r="38" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C38" s="37">
@@ -6320,10 +6320,10 @@
       <c r="F39" s="3"/>
       <c r="G39" s="43"/>
       <c r="H39" s="46"/>
-      <c r="I39" s="154" t="s">
+      <c r="I39" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="155"/>
+      <c r="J39" s="147"/>
     </row>
     <row r="40" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="37"/>
@@ -6332,8 +6332,8 @@
       <c r="F40" s="3"/>
       <c r="G40" s="43"/>
       <c r="H40" s="46"/>
-      <c r="I40" s="156"/>
-      <c r="J40" s="157"/>
+      <c r="I40" s="148"/>
+      <c r="J40" s="149"/>
     </row>
     <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="37"/>
@@ -6342,8 +6342,8 @@
       <c r="F41" s="3"/>
       <c r="G41" s="43"/>
       <c r="H41" s="46"/>
-      <c r="I41" s="156"/>
-      <c r="J41" s="157"/>
+      <c r="I41" s="148"/>
+      <c r="J41" s="149"/>
     </row>
     <row r="42" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="37"/>
@@ -6352,8 +6352,8 @@
       <c r="F42" s="3"/>
       <c r="G42" s="43"/>
       <c r="H42" s="46"/>
-      <c r="I42" s="156"/>
-      <c r="J42" s="157"/>
+      <c r="I42" s="148"/>
+      <c r="J42" s="149"/>
     </row>
     <row r="43" spans="3:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C43" s="37"/>
@@ -6362,8 +6362,8 @@
       <c r="F43" s="3"/>
       <c r="G43" s="43"/>
       <c r="H43" s="46"/>
-      <c r="I43" s="158"/>
-      <c r="J43" s="159"/>
+      <c r="I43" s="150"/>
+      <c r="J43" s="151"/>
     </row>
     <row r="44" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C44" s="37">
@@ -6394,10 +6394,10 @@
       <c r="F45" s="3"/>
       <c r="G45" s="43"/>
       <c r="H45" s="46"/>
-      <c r="I45" s="154" t="s">
+      <c r="I45" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="J45" s="155"/>
+      <c r="J45" s="147"/>
     </row>
     <row r="46" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="37"/>
@@ -6406,8 +6406,8 @@
       <c r="F46" s="3"/>
       <c r="G46" s="43"/>
       <c r="H46" s="46"/>
-      <c r="I46" s="156"/>
-      <c r="J46" s="157"/>
+      <c r="I46" s="148"/>
+      <c r="J46" s="149"/>
     </row>
     <row r="47" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="37"/>
@@ -6416,8 +6416,8 @@
       <c r="F47" s="3"/>
       <c r="G47" s="43"/>
       <c r="H47" s="46"/>
-      <c r="I47" s="156"/>
-      <c r="J47" s="157"/>
+      <c r="I47" s="148"/>
+      <c r="J47" s="149"/>
     </row>
     <row r="48" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="37"/>
@@ -6426,8 +6426,8 @@
       <c r="F48" s="3"/>
       <c r="G48" s="43"/>
       <c r="H48" s="46"/>
-      <c r="I48" s="156"/>
-      <c r="J48" s="157"/>
+      <c r="I48" s="148"/>
+      <c r="J48" s="149"/>
     </row>
     <row r="49" spans="3:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C49" s="37"/>
@@ -6436,8 +6436,8 @@
       <c r="F49" s="3"/>
       <c r="G49" s="43"/>
       <c r="H49" s="46"/>
-      <c r="I49" s="158"/>
-      <c r="J49" s="159"/>
+      <c r="I49" s="150"/>
+      <c r="J49" s="151"/>
     </row>
     <row r="50" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C50" s="37">
@@ -6468,10 +6468,10 @@
       <c r="F51" s="3"/>
       <c r="G51" s="43"/>
       <c r="H51" s="46"/>
-      <c r="I51" s="154" t="s">
+      <c r="I51" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="J51" s="155"/>
+      <c r="J51" s="147"/>
     </row>
     <row r="52" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="37"/>
@@ -6480,8 +6480,8 @@
       <c r="F52" s="3"/>
       <c r="G52" s="43"/>
       <c r="H52" s="46"/>
-      <c r="I52" s="156"/>
-      <c r="J52" s="157"/>
+      <c r="I52" s="148"/>
+      <c r="J52" s="149"/>
     </row>
     <row r="53" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="37"/>
@@ -6490,8 +6490,8 @@
       <c r="F53" s="3"/>
       <c r="G53" s="43"/>
       <c r="H53" s="46"/>
-      <c r="I53" s="156"/>
-      <c r="J53" s="157"/>
+      <c r="I53" s="148"/>
+      <c r="J53" s="149"/>
     </row>
     <row r="54" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="37"/>
@@ -6500,8 +6500,8 @@
       <c r="F54" s="3"/>
       <c r="G54" s="43"/>
       <c r="H54" s="46"/>
-      <c r="I54" s="156"/>
-      <c r="J54" s="157"/>
+      <c r="I54" s="148"/>
+      <c r="J54" s="149"/>
     </row>
     <row r="55" spans="3:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C55" s="37"/>
@@ -6510,8 +6510,8 @@
       <c r="F55" s="3"/>
       <c r="G55" s="43"/>
       <c r="H55" s="46"/>
-      <c r="I55" s="158"/>
-      <c r="J55" s="159"/>
+      <c r="I55" s="150"/>
+      <c r="J55" s="151"/>
     </row>
     <row r="56" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C56" s="37">
@@ -6540,10 +6540,10 @@
       <c r="F57" s="3"/>
       <c r="G57" s="43"/>
       <c r="H57" s="46"/>
-      <c r="I57" s="154" t="s">
+      <c r="I57" s="146" t="s">
         <v>42</v>
       </c>
-      <c r="J57" s="155"/>
+      <c r="J57" s="147"/>
     </row>
     <row r="58" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C58" s="37"/>
@@ -6552,8 +6552,8 @@
       <c r="F58" s="3"/>
       <c r="G58" s="43"/>
       <c r="H58" s="46"/>
-      <c r="I58" s="156"/>
-      <c r="J58" s="157"/>
+      <c r="I58" s="148"/>
+      <c r="J58" s="149"/>
     </row>
     <row r="59" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C59" s="37"/>
@@ -6562,8 +6562,8 @@
       <c r="F59" s="3"/>
       <c r="G59" s="43"/>
       <c r="H59" s="46"/>
-      <c r="I59" s="156"/>
-      <c r="J59" s="157"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="149"/>
     </row>
     <row r="60" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C60" s="37"/>
@@ -6572,8 +6572,8 @@
       <c r="F60" s="3"/>
       <c r="G60" s="43"/>
       <c r="H60" s="46"/>
-      <c r="I60" s="156"/>
-      <c r="J60" s="157"/>
+      <c r="I60" s="148"/>
+      <c r="J60" s="149"/>
     </row>
     <row r="61" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C61" s="37"/>
@@ -6582,8 +6582,8 @@
       <c r="F61" s="3"/>
       <c r="G61" s="43"/>
       <c r="H61" s="46"/>
-      <c r="I61" s="158"/>
-      <c r="J61" s="159"/>
+      <c r="I61" s="150"/>
+      <c r="J61" s="151"/>
     </row>
     <row r="62" spans="3:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C62" s="39">
@@ -6615,10 +6615,10 @@
       <c r="F63" s="3"/>
       <c r="G63" s="43"/>
       <c r="H63" s="46"/>
-      <c r="I63" s="154" t="s">
+      <c r="I63" s="146" t="s">
         <v>42</v>
       </c>
-      <c r="J63" s="155"/>
+      <c r="J63" s="147"/>
     </row>
     <row r="64" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C64" s="39"/>
@@ -6627,8 +6627,8 @@
       <c r="F64" s="3"/>
       <c r="G64" s="43"/>
       <c r="H64" s="46"/>
-      <c r="I64" s="156"/>
-      <c r="J64" s="157"/>
+      <c r="I64" s="148"/>
+      <c r="J64" s="149"/>
     </row>
     <row r="65" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C65" s="39"/>
@@ -6637,8 +6637,8 @@
       <c r="F65" s="3"/>
       <c r="G65" s="43"/>
       <c r="H65" s="46"/>
-      <c r="I65" s="156"/>
-      <c r="J65" s="157"/>
+      <c r="I65" s="148"/>
+      <c r="J65" s="149"/>
     </row>
     <row r="66" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C66" s="39"/>
@@ -6647,8 +6647,8 @@
       <c r="F66" s="3"/>
       <c r="G66" s="43"/>
       <c r="H66" s="46"/>
-      <c r="I66" s="156"/>
-      <c r="J66" s="157"/>
+      <c r="I66" s="148"/>
+      <c r="J66" s="149"/>
     </row>
     <row r="67" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C67" s="39"/>
@@ -6657,8 +6657,8 @@
       <c r="F67" s="3"/>
       <c r="G67" s="43"/>
       <c r="H67" s="46"/>
-      <c r="I67" s="158"/>
-      <c r="J67" s="159"/>
+      <c r="I67" s="150"/>
+      <c r="J67" s="151"/>
     </row>
     <row r="68" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C68" s="39"/>
@@ -6701,10 +6701,10 @@
       <c r="F70" s="98"/>
       <c r="G70" s="97"/>
       <c r="H70" s="102"/>
-      <c r="I70" s="160" t="s">
+      <c r="I70" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="J70" s="161"/>
+      <c r="J70" s="153"/>
     </row>
     <row r="71" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="37"/>
@@ -6713,8 +6713,8 @@
       <c r="F71" s="98"/>
       <c r="G71" s="97"/>
       <c r="H71" s="102"/>
-      <c r="I71" s="162"/>
-      <c r="J71" s="163"/>
+      <c r="I71" s="154"/>
+      <c r="J71" s="155"/>
     </row>
     <row r="72" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="37"/>
@@ -6723,8 +6723,8 @@
       <c r="F72" s="98"/>
       <c r="G72" s="97"/>
       <c r="H72" s="102"/>
-      <c r="I72" s="162"/>
-      <c r="J72" s="163"/>
+      <c r="I72" s="154"/>
+      <c r="J72" s="155"/>
     </row>
     <row r="73" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="37"/>
@@ -6733,8 +6733,8 @@
       <c r="F73" s="98"/>
       <c r="G73" s="97"/>
       <c r="H73" s="102"/>
-      <c r="I73" s="162"/>
-      <c r="J73" s="163"/>
+      <c r="I73" s="154"/>
+      <c r="J73" s="155"/>
     </row>
     <row r="74" spans="3:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C74" s="37"/>
@@ -6743,8 +6743,8 @@
       <c r="F74" s="98"/>
       <c r="G74" s="97"/>
       <c r="H74" s="102"/>
-      <c r="I74" s="164"/>
-      <c r="J74" s="165"/>
+      <c r="I74" s="156"/>
+      <c r="J74" s="157"/>
     </row>
     <row r="75" spans="3:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C75" s="37">
@@ -6777,10 +6777,10 @@
       <c r="F76" s="98"/>
       <c r="G76" s="97"/>
       <c r="H76" s="102"/>
-      <c r="I76" s="160" t="s">
+      <c r="I76" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="J76" s="161"/>
+      <c r="J76" s="153"/>
     </row>
     <row r="77" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C77" s="37"/>
@@ -6789,8 +6789,8 @@
       <c r="F77" s="98"/>
       <c r="G77" s="97"/>
       <c r="H77" s="102"/>
-      <c r="I77" s="162"/>
-      <c r="J77" s="163"/>
+      <c r="I77" s="154"/>
+      <c r="J77" s="155"/>
     </row>
     <row r="78" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="37"/>
@@ -6799,8 +6799,8 @@
       <c r="F78" s="98"/>
       <c r="G78" s="97"/>
       <c r="H78" s="102"/>
-      <c r="I78" s="162"/>
-      <c r="J78" s="163"/>
+      <c r="I78" s="154"/>
+      <c r="J78" s="155"/>
     </row>
     <row r="79" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C79" s="37"/>
@@ -6809,8 +6809,8 @@
       <c r="F79" s="98"/>
       <c r="G79" s="97"/>
       <c r="H79" s="102"/>
-      <c r="I79" s="162"/>
-      <c r="J79" s="163"/>
+      <c r="I79" s="154"/>
+      <c r="J79" s="155"/>
     </row>
     <row r="80" spans="3:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C80" s="37"/>
@@ -6819,8 +6819,8 @@
       <c r="F80" s="98"/>
       <c r="G80" s="97"/>
       <c r="H80" s="102"/>
-      <c r="I80" s="164"/>
-      <c r="J80" s="165"/>
+      <c r="I80" s="156"/>
+      <c r="J80" s="157"/>
     </row>
     <row r="81" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C81" s="37">
@@ -6851,10 +6851,10 @@
       <c r="F82" s="3"/>
       <c r="G82" s="43"/>
       <c r="H82" s="46"/>
-      <c r="I82" s="170" t="s">
+      <c r="I82" s="173" t="s">
         <v>39</v>
       </c>
-      <c r="J82" s="171"/>
+      <c r="J82" s="174"/>
     </row>
     <row r="83" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C83" s="37"/>
@@ -6863,8 +6863,8 @@
       <c r="F83" s="3"/>
       <c r="G83" s="43"/>
       <c r="H83" s="46"/>
-      <c r="I83" s="172"/>
-      <c r="J83" s="173"/>
+      <c r="I83" s="175"/>
+      <c r="J83" s="176"/>
     </row>
     <row r="84" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C84" s="37"/>
@@ -6873,8 +6873,8 @@
       <c r="F84" s="3"/>
       <c r="G84" s="43"/>
       <c r="H84" s="46"/>
-      <c r="I84" s="172"/>
-      <c r="J84" s="173"/>
+      <c r="I84" s="175"/>
+      <c r="J84" s="176"/>
     </row>
     <row r="85" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C85" s="37"/>
@@ -6883,8 +6883,8 @@
       <c r="F85" s="3"/>
       <c r="G85" s="43"/>
       <c r="H85" s="46"/>
-      <c r="I85" s="172"/>
-      <c r="J85" s="173"/>
+      <c r="I85" s="175"/>
+      <c r="J85" s="176"/>
     </row>
     <row r="86" spans="3:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C86" s="37"/>
@@ -6893,8 +6893,8 @@
       <c r="F86" s="3"/>
       <c r="G86" s="43"/>
       <c r="H86" s="46"/>
-      <c r="I86" s="174"/>
-      <c r="J86" s="175"/>
+      <c r="I86" s="177"/>
+      <c r="J86" s="178"/>
     </row>
     <row r="87" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C87" s="37">
@@ -6923,10 +6923,10 @@
       <c r="F88" s="3"/>
       <c r="G88" s="43"/>
       <c r="H88" s="46"/>
-      <c r="I88" s="154" t="s">
+      <c r="I88" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="J88" s="155"/>
+      <c r="J88" s="147"/>
     </row>
     <row r="89" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C89" s="37"/>
@@ -6935,8 +6935,8 @@
       <c r="F89" s="3"/>
       <c r="G89" s="43"/>
       <c r="H89" s="46"/>
-      <c r="I89" s="156"/>
-      <c r="J89" s="157"/>
+      <c r="I89" s="148"/>
+      <c r="J89" s="149"/>
     </row>
     <row r="90" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="37"/>
@@ -6945,8 +6945,8 @@
       <c r="F90" s="3"/>
       <c r="G90" s="43"/>
       <c r="H90" s="46"/>
-      <c r="I90" s="156"/>
-      <c r="J90" s="157"/>
+      <c r="I90" s="148"/>
+      <c r="J90" s="149"/>
     </row>
     <row r="91" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C91" s="37"/>
@@ -6955,8 +6955,8 @@
       <c r="F91" s="3"/>
       <c r="G91" s="43"/>
       <c r="H91" s="46"/>
-      <c r="I91" s="156"/>
-      <c r="J91" s="157"/>
+      <c r="I91" s="148"/>
+      <c r="J91" s="149"/>
     </row>
     <row r="92" spans="3:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C92" s="37"/>
@@ -6965,8 +6965,8 @@
       <c r="F92" s="3"/>
       <c r="G92" s="43"/>
       <c r="H92" s="46"/>
-      <c r="I92" s="158"/>
-      <c r="J92" s="159"/>
+      <c r="I92" s="150"/>
+      <c r="J92" s="151"/>
     </row>
     <row r="93" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C93" s="37">
@@ -6995,10 +6995,10 @@
       <c r="F94" s="3"/>
       <c r="G94" s="43"/>
       <c r="H94" s="43"/>
-      <c r="I94" s="154" t="s">
+      <c r="I94" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="J94" s="155"/>
+      <c r="J94" s="147"/>
     </row>
     <row r="95" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C95" s="37"/>
@@ -7007,8 +7007,8 @@
       <c r="F95" s="3"/>
       <c r="G95" s="43"/>
       <c r="H95" s="46"/>
-      <c r="I95" s="156"/>
-      <c r="J95" s="157"/>
+      <c r="I95" s="148"/>
+      <c r="J95" s="149"/>
     </row>
     <row r="96" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C96" s="37"/>
@@ -7017,8 +7017,8 @@
       <c r="F96" s="3"/>
       <c r="G96" s="43"/>
       <c r="H96" s="46"/>
-      <c r="I96" s="156"/>
-      <c r="J96" s="157"/>
+      <c r="I96" s="148"/>
+      <c r="J96" s="149"/>
     </row>
     <row r="97" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C97" s="37"/>
@@ -7027,8 +7027,8 @@
       <c r="F97" s="3"/>
       <c r="G97" s="43"/>
       <c r="H97" s="46"/>
-      <c r="I97" s="156"/>
-      <c r="J97" s="157"/>
+      <c r="I97" s="148"/>
+      <c r="J97" s="149"/>
     </row>
     <row r="98" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C98" s="37"/>
@@ -7037,8 +7037,8 @@
       <c r="F98" s="3"/>
       <c r="G98" s="43"/>
       <c r="H98" s="46"/>
-      <c r="I98" s="158"/>
-      <c r="J98" s="159"/>
+      <c r="I98" s="150"/>
+      <c r="J98" s="151"/>
     </row>
     <row r="99" spans="3:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C99" s="37">
@@ -7071,10 +7071,10 @@
       <c r="F100" s="3"/>
       <c r="G100" s="43"/>
       <c r="H100" s="46"/>
-      <c r="I100" s="154" t="s">
+      <c r="I100" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="J100" s="155"/>
+      <c r="J100" s="147"/>
     </row>
     <row r="101" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C101" s="37"/>
@@ -7083,8 +7083,8 @@
       <c r="F101" s="3"/>
       <c r="G101" s="43"/>
       <c r="H101" s="46"/>
-      <c r="I101" s="156"/>
-      <c r="J101" s="157"/>
+      <c r="I101" s="148"/>
+      <c r="J101" s="149"/>
     </row>
     <row r="102" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C102" s="37"/>
@@ -7093,8 +7093,8 @@
       <c r="F102" s="3"/>
       <c r="G102" s="43"/>
       <c r="H102" s="46"/>
-      <c r="I102" s="156"/>
-      <c r="J102" s="157"/>
+      <c r="I102" s="148"/>
+      <c r="J102" s="149"/>
     </row>
     <row r="103" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C103" s="37"/>
@@ -7103,8 +7103,8 @@
       <c r="F103" s="3"/>
       <c r="G103" s="43"/>
       <c r="H103" s="46"/>
-      <c r="I103" s="156"/>
-      <c r="J103" s="157"/>
+      <c r="I103" s="148"/>
+      <c r="J103" s="149"/>
     </row>
     <row r="104" spans="3:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C104" s="37"/>
@@ -7113,8 +7113,8 @@
       <c r="F104" s="3"/>
       <c r="G104" s="43"/>
       <c r="H104" s="46"/>
-      <c r="I104" s="158"/>
-      <c r="J104" s="159"/>
+      <c r="I104" s="150"/>
+      <c r="J104" s="151"/>
     </row>
     <row r="105" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C105" s="37">
@@ -7143,10 +7143,10 @@
       <c r="F106" s="3"/>
       <c r="G106" s="43"/>
       <c r="H106" s="43"/>
-      <c r="I106" s="154" t="s">
+      <c r="I106" s="146" t="s">
         <v>42</v>
       </c>
-      <c r="J106" s="155"/>
+      <c r="J106" s="147"/>
     </row>
     <row r="107" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C107" s="37"/>
@@ -7155,8 +7155,8 @@
       <c r="F107" s="3"/>
       <c r="G107" s="43"/>
       <c r="H107" s="46"/>
-      <c r="I107" s="156"/>
-      <c r="J107" s="157"/>
+      <c r="I107" s="148"/>
+      <c r="J107" s="149"/>
     </row>
     <row r="108" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C108" s="37"/>
@@ -7165,8 +7165,8 @@
       <c r="F108" s="3"/>
       <c r="G108" s="43"/>
       <c r="H108" s="46"/>
-      <c r="I108" s="156"/>
-      <c r="J108" s="157"/>
+      <c r="I108" s="148"/>
+      <c r="J108" s="149"/>
     </row>
     <row r="109" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C109" s="37"/>
@@ -7175,8 +7175,8 @@
       <c r="F109" s="3"/>
       <c r="G109" s="43"/>
       <c r="H109" s="46"/>
-      <c r="I109" s="156"/>
-      <c r="J109" s="157"/>
+      <c r="I109" s="148"/>
+      <c r="J109" s="149"/>
     </row>
     <row r="110" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C110" s="37"/>
@@ -7185,8 +7185,8 @@
       <c r="F110" s="3"/>
       <c r="G110" s="43"/>
       <c r="H110" s="46"/>
-      <c r="I110" s="158"/>
-      <c r="J110" s="159"/>
+      <c r="I110" s="150"/>
+      <c r="J110" s="151"/>
     </row>
     <row r="111" spans="3:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C111" s="37">
@@ -7218,10 +7218,10 @@
       <c r="F112" s="3"/>
       <c r="G112" s="43"/>
       <c r="H112" s="46"/>
-      <c r="I112" s="154" t="s">
+      <c r="I112" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="J112" s="155"/>
+      <c r="J112" s="147"/>
     </row>
     <row r="113" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C113" s="37"/>
@@ -7230,8 +7230,8 @@
       <c r="F113" s="3"/>
       <c r="G113" s="43"/>
       <c r="H113" s="43"/>
-      <c r="I113" s="156"/>
-      <c r="J113" s="157"/>
+      <c r="I113" s="148"/>
+      <c r="J113" s="149"/>
       <c r="K113" s="118"/>
     </row>
     <row r="114" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7241,8 +7241,8 @@
       <c r="F114" s="3"/>
       <c r="G114" s="43"/>
       <c r="H114" s="43"/>
-      <c r="I114" s="156"/>
-      <c r="J114" s="157"/>
+      <c r="I114" s="148"/>
+      <c r="J114" s="149"/>
       <c r="K114" s="116" t="s">
         <v>78</v>
       </c>
@@ -7254,8 +7254,8 @@
       <c r="F115" s="3"/>
       <c r="G115" s="43"/>
       <c r="H115" s="43"/>
-      <c r="I115" s="156"/>
-      <c r="J115" s="157"/>
+      <c r="I115" s="148"/>
+      <c r="J115" s="149"/>
       <c r="K115" s="117"/>
     </row>
     <row r="116" spans="3:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7265,8 +7265,8 @@
       <c r="F116" s="3"/>
       <c r="G116" s="43"/>
       <c r="H116" s="43"/>
-      <c r="I116" s="158"/>
-      <c r="J116" s="159"/>
+      <c r="I116" s="150"/>
+      <c r="J116" s="151"/>
       <c r="K116" s="116" t="s">
         <v>80</v>
       </c>
@@ -7298,10 +7298,10 @@
       <c r="F118" s="3"/>
       <c r="G118" s="43"/>
       <c r="H118" s="46"/>
-      <c r="I118" s="160" t="s">
+      <c r="I118" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J118" s="161"/>
+      <c r="J118" s="153"/>
     </row>
     <row r="119" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C119" s="37"/>
@@ -7310,8 +7310,8 @@
       <c r="F119" s="3"/>
       <c r="G119" s="43"/>
       <c r="H119" s="43"/>
-      <c r="I119" s="162"/>
-      <c r="J119" s="163"/>
+      <c r="I119" s="154"/>
+      <c r="J119" s="155"/>
     </row>
     <row r="120" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C120" s="37"/>
@@ -7320,8 +7320,8 @@
       <c r="F120" s="3"/>
       <c r="G120" s="43"/>
       <c r="H120" s="43"/>
-      <c r="I120" s="162"/>
-      <c r="J120" s="163"/>
+      <c r="I120" s="154"/>
+      <c r="J120" s="155"/>
     </row>
     <row r="121" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C121" s="37"/>
@@ -7330,8 +7330,8 @@
       <c r="F121" s="3"/>
       <c r="G121" s="43"/>
       <c r="H121" s="43"/>
-      <c r="I121" s="162"/>
-      <c r="J121" s="163"/>
+      <c r="I121" s="154"/>
+      <c r="J121" s="155"/>
     </row>
     <row r="122" spans="3:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C122" s="37"/>
@@ -7340,8 +7340,8 @@
       <c r="F122" s="3"/>
       <c r="G122" s="43"/>
       <c r="H122" s="43"/>
-      <c r="I122" s="164"/>
-      <c r="J122" s="165"/>
+      <c r="I122" s="156"/>
+      <c r="J122" s="157"/>
     </row>
     <row r="123" spans="3:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C123" s="37">
@@ -7364,8 +7364,8 @@
       <c r="H123" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I123" s="168"/>
-      <c r="J123" s="169"/>
+      <c r="I123" s="171"/>
+      <c r="J123" s="172"/>
     </row>
     <row r="124" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C124" s="37"/>
@@ -7374,10 +7374,10 @@
       <c r="F124" s="3"/>
       <c r="G124" s="43"/>
       <c r="H124" s="47"/>
-      <c r="I124" s="146" t="s">
+      <c r="I124" s="161" t="s">
         <v>46</v>
       </c>
-      <c r="J124" s="147"/>
+      <c r="J124" s="162"/>
     </row>
     <row r="125" spans="3:11" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C125" s="37"/>
@@ -7386,8 +7386,8 @@
       <c r="F125" s="3"/>
       <c r="G125" s="43"/>
       <c r="H125" s="47"/>
-      <c r="I125" s="148"/>
-      <c r="J125" s="149"/>
+      <c r="I125" s="163"/>
+      <c r="J125" s="164"/>
       <c r="K125" s="116" t="s">
         <v>79</v>
       </c>
@@ -7399,8 +7399,8 @@
       <c r="F126" s="3"/>
       <c r="G126" s="43"/>
       <c r="H126" s="47"/>
-      <c r="I126" s="148"/>
-      <c r="J126" s="149"/>
+      <c r="I126" s="163"/>
+      <c r="J126" s="164"/>
       <c r="K126" s="117"/>
     </row>
     <row r="127" spans="3:11" ht="20.25" x14ac:dyDescent="0.3">
@@ -7410,8 +7410,8 @@
       <c r="F127" s="3"/>
       <c r="G127" s="43"/>
       <c r="H127" s="47"/>
-      <c r="I127" s="148"/>
-      <c r="J127" s="149"/>
+      <c r="I127" s="163"/>
+      <c r="J127" s="164"/>
       <c r="K127" s="116" t="s">
         <v>80</v>
       </c>
@@ -7423,8 +7423,8 @@
       <c r="F128" s="3"/>
       <c r="G128" s="43"/>
       <c r="H128" s="47"/>
-      <c r="I128" s="150"/>
-      <c r="J128" s="151"/>
+      <c r="I128" s="165"/>
+      <c r="J128" s="166"/>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C129" s="37"/>
@@ -7457,10 +7457,10 @@
       <c r="H130" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="I130" s="166" t="s">
+      <c r="I130" s="169" t="s">
         <v>48</v>
       </c>
-      <c r="J130" s="167"/>
+      <c r="J130" s="170"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C131" s="37">
@@ -7483,10 +7483,10 @@
       <c r="H131" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="I131" s="152" t="s">
+      <c r="I131" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="J131" s="153"/>
+      <c r="J131" s="168"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C132" s="39">
@@ -7535,18 +7535,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="I57:J61"/>
-    <mergeCell ref="I70:J74"/>
-    <mergeCell ref="I63:J67"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="I6:J10"/>
-    <mergeCell ref="I14:J18"/>
-    <mergeCell ref="I20:J24"/>
-    <mergeCell ref="I26:J30"/>
-    <mergeCell ref="I33:J37"/>
     <mergeCell ref="O10:P10"/>
     <mergeCell ref="I124:J128"/>
     <mergeCell ref="I131:J131"/>
@@ -7563,6 +7551,18 @@
     <mergeCell ref="I39:J43"/>
     <mergeCell ref="I45:J49"/>
     <mergeCell ref="I51:J55"/>
+    <mergeCell ref="I57:J61"/>
+    <mergeCell ref="I70:J74"/>
+    <mergeCell ref="I63:J67"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="I6:J10"/>
+    <mergeCell ref="I14:J18"/>
+    <mergeCell ref="I20:J24"/>
+    <mergeCell ref="I26:J30"/>
+    <mergeCell ref="I33:J37"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C134" r:id="rId1" display="https://www.vd.ch/themes/formation/jours-feries-et-vacances-scolaires" xr:uid="{821AA856-928F-498C-8735-8AED53396F8C}"/>
